--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -632,7 +632,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -657,7 +660,13 @@
     <t>内視鏡検査の第1カテゴリはJP_SimpleObservationCategory_VSからprocedureを指定する。</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -913,10 +922,13 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationCategory_Endoscopy_VS</t>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetは指定しない。</t>
+  </si>
+  <si>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetのバインディングを指定していないことに注意すること。</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -1296,10 +1308,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -2040,7 +2049,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.69140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.41015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3817,22 +3826,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>190</v>
@@ -3859,10 +3870,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3870,13 +3881,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3886,7 +3897,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3901,13 +3912,13 @@
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>196</v>
@@ -3939,7 +3950,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3981,10 +3992,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3992,10 +4003,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4018,13 +4029,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4075,7 +4086,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4099,7 +4110,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4110,10 +4121,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4142,7 +4153,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4183,19 +4194,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4219,7 +4230,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4230,10 +4241,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4256,19 +4267,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4317,7 +4328,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4338,10 +4349,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4352,10 +4363,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4378,13 +4389,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4435,7 +4446,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4459,7 +4470,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4470,10 +4481,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4502,7 +4513,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4543,19 +4554,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4579,7 +4590,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4590,10 +4601,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4619,23 +4630,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4677,7 +4688,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4698,10 +4709,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4712,10 +4723,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4738,16 +4749,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4797,7 +4808,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4818,10 +4829,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4832,10 +4843,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4861,21 +4872,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4917,7 +4928,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4938,10 +4949,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4952,10 +4963,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4978,17 +4989,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5037,7 +5048,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5058,10 +5069,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5072,10 +5083,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5098,19 +5109,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5159,7 +5170,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5180,10 +5191,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5194,10 +5205,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5220,19 +5231,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5281,7 +5292,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5302,10 +5313,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5316,13 +5327,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5347,13 +5358,13 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>196</v>
@@ -5381,11 +5392,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5427,10 +5440,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5438,10 +5451,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5464,13 +5477,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5521,7 +5534,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5545,7 +5558,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5556,10 +5569,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5588,7 +5601,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5629,19 +5642,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5665,7 +5678,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5676,10 +5689,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5702,19 +5715,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5763,7 +5776,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5784,10 +5797,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5798,10 +5811,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5824,13 +5837,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5881,7 +5894,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5905,7 +5918,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5916,10 +5929,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5948,7 +5961,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5989,19 +6002,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6025,7 +6038,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6036,10 +6049,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6065,23 +6078,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6123,7 +6136,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6144,10 +6157,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6158,10 +6171,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6184,16 +6197,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6243,7 +6256,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6264,10 +6277,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6278,10 +6291,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6307,21 +6320,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6363,7 +6376,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6384,10 +6397,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6398,10 +6411,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6424,17 +6437,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6483,7 +6496,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6504,10 +6517,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6518,10 +6531,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6544,19 +6557,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6605,7 +6618,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6626,10 +6639,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6640,10 +6653,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6666,19 +6679,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6727,7 +6740,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6748,10 +6761,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6762,14 +6775,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6791,16 +6804,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6829,7 +6842,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6847,7 +6860,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6862,30 +6875,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6908,19 +6921,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6969,7 +6982,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6984,19 +6997,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7004,10 +7017,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7030,16 +7043,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7089,7 +7102,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7110,13 +7123,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7124,14 +7137,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7150,19 +7163,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7211,7 +7224,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7226,19 +7239,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7246,14 +7259,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7272,19 +7285,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7333,7 +7346,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7348,19 +7361,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7368,10 +7381,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7394,16 +7407,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7453,7 +7466,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7474,13 +7487,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7488,10 +7501,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7514,19 +7527,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7575,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7590,19 +7603,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7610,10 +7623,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7636,19 +7649,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7673,11 +7686,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7695,7 +7708,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7704,7 +7717,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7713,27 +7726,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7759,16 +7772,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7793,31 +7806,31 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7826,7 +7839,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7841,7 +7854,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7852,14 +7865,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7881,16 +7894,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7915,13 +7928,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7939,7 +7952,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7957,27 +7970,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8000,19 +8013,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8061,7 +8074,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8082,10 +8095,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8096,10 +8109,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8125,13 +8138,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8157,31 +8170,29 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8199,27 +8210,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8245,16 +8256,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8279,13 +8290,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8303,7 +8314,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8324,10 +8335,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8338,10 +8349,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8364,16 +8375,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8423,7 +8434,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8441,27 +8452,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8484,16 +8495,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8543,7 +8554,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8561,27 +8572,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8604,19 +8615,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8665,7 +8676,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8677,7 +8688,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8686,10 +8697,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8700,10 +8711,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8726,13 +8737,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8783,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8807,7 +8818,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8818,10 +8829,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8850,7 +8861,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8903,7 +8914,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8927,7 +8938,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8938,14 +8949,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8967,10 +8978,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9025,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9060,10 +9071,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9086,13 +9097,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9143,7 +9154,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9152,7 +9163,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9164,10 +9175,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9178,10 +9189,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9204,13 +9215,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9261,7 +9272,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9270,7 +9281,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9282,10 +9293,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9296,10 +9307,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9325,16 +9336,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9362,10 +9373,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9383,7 +9394,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9401,13 +9412,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9418,10 +9429,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9447,16 +9458,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9481,13 +9492,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9505,7 +9516,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9523,13 +9534,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9540,10 +9551,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9566,17 +9577,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9625,7 +9636,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9649,7 +9660,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9660,10 +9671,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9686,13 +9697,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9743,7 +9754,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9764,10 +9775,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9778,10 +9789,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9804,16 +9815,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9863,7 +9874,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9884,10 +9895,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9898,10 +9909,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9924,16 +9935,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9983,7 +9994,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10004,10 +10015,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10018,10 +10029,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10044,19 +10055,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10105,7 +10116,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10126,10 +10137,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10140,10 +10151,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10166,13 +10177,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10223,7 +10234,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10247,7 +10258,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10258,10 +10269,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10290,7 +10301,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10343,7 +10354,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10367,7 +10378,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10378,14 +10389,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10407,10 +10418,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10465,7 +10476,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10500,10 +10511,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10529,16 +10540,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10563,13 +10574,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10587,7 +10598,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10605,16 +10616,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10622,10 +10633,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10648,19 +10659,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10709,7 +10720,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10727,27 +10738,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10773,16 +10784,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10807,13 +10818,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10831,7 +10842,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10840,7 +10851,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10855,7 +10866,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10866,14 +10877,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10895,16 +10906,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10929,13 +10940,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10953,7 +10964,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10971,27 +10982,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11017,16 +11028,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11075,7 +11086,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11096,10 +11107,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
